--- a/data/accounting_templates/accounting_templates.xlsx
+++ b/data/accounting_templates/accounting_templates.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductUnitCosts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductCosts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WriteOffs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLAccounts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,47 +430,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>expense_date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>receipt_url</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -474,24 +484,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Hydro One</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Silicone molds</t>
+          <t>Shop electricity bill</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29.99</v>
+        <v>145.22</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>18.88</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -516,32 +526,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>unit_cost</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -549,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1000</v>
+        <v>101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -564,10 +574,14 @@
           <t>CAD</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Initial unit cost estimate</t>
+          <t>Current direct unit cost</t>
         </is>
       </c>
     </row>
@@ -586,47 +600,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>writeoff_date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reference_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>writeoff_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>gl_account_code</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -640,32 +654,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expense</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Damaged inventory write-off</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Damaged pendant</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>damage</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>101</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Dropped during finishing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -678,21 +698,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>parent_group</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>normal_balance</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -701,68 +741,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>clay, wax, sand, resin</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumables used for production</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>burs, bits, saw blades</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Longer-lived tools; decide capitalization later</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Shipping</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>postage, boxes, labels</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Direct fulfillment costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>kiln, compressor</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>May be capital asset depending on policy</t>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>debit</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Shop hydro</t>
         </is>
       </c>
     </row>

--- a/data/accounting_templates/accounting_templates.xlsx
+++ b/data/accounting_templates/accounting_templates.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductCosts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GL Accounts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WriteOffs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLAccounts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductCosts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,22 +28,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,90 +416,338 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>expense_date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>vendor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>receipt_url</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>is_active</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hydro One</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>expense</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shop electricity bill</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>145.22</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18.88</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6120</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Software Subscriptions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6700</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Equipment &amp; Tools</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6810</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Workshop Consumables</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Write-Offs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -526,62 +764,66 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>unit_cost</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>vendor</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>expense_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>vendor_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tax_amount</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ledger_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>101</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>12.5</v>
+          <t>Hydro One</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>125.50</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Current direct unit cost</t>
+          <t>Monthly workshop electricity</t>
         </is>
       </c>
     </row>
@@ -596,51 +838,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>writeoff_date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>writeoff_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>item_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>gl_account_code</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>reason_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -649,41 +871,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>Broken mold</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Damaged pendant</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>12.5</v>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>damaged</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>6900</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>101</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Dropped during finishing</t>
+          <t>Discarded after failure</t>
         </is>
       </c>
     </row>
@@ -698,41 +906,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>parent_group</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>normal_balance</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sort_order</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>product_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cost_per_unit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>effective_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -741,35 +934,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>DD1000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>debit</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Shop hydro</t>
+          <t>Material + labour + overhead estimate</t>
         </is>
       </c>
     </row>
